--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -684,21 +684,21 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>0*</t>
+          <t>2*</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>0*</t>
+          <t>5*</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>0.0*</t>
+          <t>0.08*</t>
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1</v>
+        <v>0.9998842592592593</v>
       </c>
     </row>
     <row r="19">
@@ -2128,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>100.0000%</t>
+          <t>99.9884%</t>
         </is>
       </c>
     </row>
@@ -2261,17 +2261,129 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>0.9979166666666667</v>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="12" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>0.9986111111111111</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Services Affected (to date)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Detailed Incidents (to date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>1. April 08, 2026 - Multiple Outages (3 minutes total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Service 1: Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Service 2: Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Time: 4:09 AM GMT-4:12 AM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2. April 09, 2026 - Outage (2 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Time: 7:11 PM GMT-7:13 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2337,21 +2449,21 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -2367,21 +2479,21 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -2392,30 +2504,30 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>203</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -2427,115 +2539,115 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -2547,25 +2659,25 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -2577,25 +2689,25 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -2607,21 +2719,21 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -2637,21 +2749,21 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>90</v>
+        <v>203</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -2667,21 +2779,21 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -2697,21 +2809,21 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -2727,21 +2839,21 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -2752,26 +2864,26 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -2787,21 +2899,21 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>198</v>
+        <v>123</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -2817,21 +2929,21 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>198</v>
+        <v>123</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -2842,26 +2954,26 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -2872,26 +2984,26 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -2902,26 +3014,26 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -2937,21 +3049,21 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>164</v>
+        <v>99</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -2962,26 +3074,26 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>164</v>
+        <v>3</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -2997,21 +3109,21 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -3027,21 +3139,21 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -3052,26 +3164,26 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -3082,26 +3194,26 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -3112,26 +3224,26 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -3147,21 +3259,21 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -3177,21 +3289,21 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -3207,21 +3319,21 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -3232,26 +3344,26 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -3262,26 +3374,26 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -3292,26 +3404,26 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -3322,26 +3434,26 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -3352,26 +3464,26 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -3382,30 +3494,30 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -3417,115 +3529,115 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>207</v>
+        <v>11</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>159</v>
+        <v>5</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -3537,17 +3649,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -3555,7 +3667,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -3567,51 +3679,51 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>282</v>
+        <v>5</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
@@ -3627,21 +3739,21 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>282</v>
+        <v>207</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -3657,21 +3769,21 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -3687,21 +3799,21 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -3717,21 +3829,21 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -3742,26 +3854,26 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -3772,26 +3884,26 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
@@ -3807,21 +3919,21 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -3837,25 +3949,25 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>4234</v>
+        <v>282</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -3867,72 +3979,72 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>4234</v>
+        <v>127</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3941,11 +4053,11 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -3957,25 +4069,25 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1595</v>
+        <v>98</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -3987,25 +4099,25 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1595</v>
+        <v>88</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -4017,51 +4129,51 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>4982</v>
+        <v>88</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>4234</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
@@ -4077,21 +4189,21 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1070</v>
+        <v>4234</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
@@ -4107,17 +4219,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-01-27T14:46:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -4137,21 +4249,21 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-01-27T14:45:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -4167,12 +4279,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -4181,7 +4293,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>140</v>
+        <v>1595</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -4197,12 +4309,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -4211,7 +4323,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>140</v>
+        <v>1595</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -4227,21 +4339,21 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-16T16:24:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>137</v>
+        <v>4982</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -4252,26 +4364,26 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-16T15:14:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -4287,21 +4399,21 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-01-15T21:13:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>38</v>
+        <v>1070</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
@@ -4312,37 +4424,247 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:24:00Z</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-10T15:08:00Z</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E75" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: April 04, 2026</t>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: April 16, 2026</t>
         </is>
       </c>
     </row>
@@ -4729,7 +5051,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: April 16, 2026 (mid-month update; April data through Apr 16, no new events since Apr 2).</t>
+          <t>Last updated: April 16, 2026 (mid-month update; April data through Apr 16; events added: Apr 7 AMS Portal degradation, Apr 8 FedRAMP outage 3 min, Apr 9 EU SAST outage 2 min, Apr 9-10 SAST maintenance windows).</t>
         </is>
       </c>
     </row>

--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="2026 Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Jan 2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Feb 2026" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mar 2026" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Apr 2026" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2026 Incident Data" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Bucket Mapping" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Notes &amp; Methodology" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Regional Breakout" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Jan 2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Feb 2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mar 2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Apr 2026" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026 Incident Data" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Bucket Mapping" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Notes &amp; Methodology" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -104,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +120,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -684,21 +694,21 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2*</t>
+          <t>4*</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>5*</t>
+          <t>25*</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>0.08*</t>
+          <t>0.42*</t>
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0.9998842592592593</v>
+        <v>0.9994212962962963</v>
       </c>
     </row>
     <row r="19">
@@ -1012,6 +1022,1286 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Regional Breakout: Per-Component Uptime</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Core Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP Portal</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>0.9999775985663082</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>0.9990367383512545</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0.9999305555555555</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="n">
+        <v>0.9996604938271605</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP API</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>0.9999775985663082</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>0.9998431899641577</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>0.9999537037037037</v>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="n">
+        <v>0.9999382716049383</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>AMS Portal</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>AMS API</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>EMEA Portal</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>EMEA API</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>APAC Portal</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>APAC API</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>SGP Portal</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>SGP API</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>0.9998759920634921</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="n">
+        <v>0.9999614197530864</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>EU Portal</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>0.9997685185185186</v>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>EU API</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>0.9997685185185186</v>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SAST Aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>AMS SAST Aviator</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>0.9999503968253968</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>0.9997535842293906</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="12" t="n">
+        <v>0.9998996913580247</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>EU SAST Aviator</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>0.9999327956989247</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>0.9999503968253968</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>0.9999551971326165</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>0.9999537037037037</v>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="n">
+        <v>0.999945987654321</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Other Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Debricked Fortify Integration</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Vulncat</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>0.9999775985663082</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="12" t="n">
+        <v>0.9999922839506172</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>* April 2026 is in progress. Partial data shown in italics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Uptime = (total_month_minutes - outage_minutes) / total_month_minutes. Only Outage events counted. No cross-component de-duplication.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1144,7 +2434,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="15" t="n">
         <v>46032</v>
       </c>
       <c r="B14" s="5" t="n">
@@ -1153,12 +2443,12 @@
       <c r="C14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.9986111111111111</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="15" t="n">
         <v>46037</v>
       </c>
       <c r="B15" s="5" t="n">
@@ -1167,12 +2457,12 @@
       <c r="C15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.9993055555555556</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="15" t="n">
         <v>46038</v>
       </c>
       <c r="B16" s="5" t="n">
@@ -1181,12 +2471,12 @@
       <c r="C16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="16" t="n">
         <v>0.9993055555555556</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="15" t="n">
         <v>46049</v>
       </c>
       <c r="B17" s="5" t="n">
@@ -1195,7 +2485,7 @@
       <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="16" t="n">
         <v>0.9993055555555556</v>
       </c>
     </row>
@@ -1365,7 +2655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1498,7 +2788,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="15" t="n">
         <v>46079</v>
       </c>
       <c r="B14" s="5" t="n">
@@ -1507,12 +2797,12 @@
       <c r="C14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.9965277777777778</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="15" t="n">
         <v>46067</v>
       </c>
       <c r="B15" s="5" t="n">
@@ -1521,12 +2811,12 @@
       <c r="C15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.9986111111111111</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="15" t="n">
         <v>46068</v>
       </c>
       <c r="B16" s="5" t="n">
@@ -1535,7 +2825,7 @@
       <c r="C16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="16" t="n">
         <v>0.9986111111111111</v>
       </c>
     </row>
@@ -1663,7 +2953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1796,7 +3086,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="15" t="n">
         <v>46083</v>
       </c>
       <c r="B14" s="5" t="n">
@@ -1805,12 +3095,12 @@
       <c r="C14" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.9694444444444444</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="15" t="n">
         <v>46092</v>
       </c>
       <c r="B15" s="5" t="n">
@@ -1819,12 +3109,12 @@
       <c r="C15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.9972222222222222</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="15" t="n">
         <v>46094</v>
       </c>
       <c r="B16" s="5" t="n">
@@ -1833,12 +3123,12 @@
       <c r="C16" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="16" t="n">
         <v>0.9972222222222222</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B17" s="5" t="n">
@@ -1847,12 +3137,12 @@
       <c r="C17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="16" t="n">
         <v>0.9979166666666667</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="15" t="n">
         <v>46098</v>
       </c>
       <c r="B18" s="5" t="n">
@@ -1861,7 +3151,7 @@
       <c r="C18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="16" t="n">
         <v>0.9986111111111111</v>
       </c>
     </row>
@@ -2122,13 +3412,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2192,7 +3482,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2204,7 +3494,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -2216,7 +3506,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>99.9884%</t>
+          <t>99.9421%</t>
         </is>
       </c>
     </row>
@@ -2262,126 +3552,210 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="15" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>0.9861111111111112</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
         <v>46120</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="5" t="n">
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D17" s="16" t="n">
         <v>0.9979166666666667</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="n">
+    <row r="18">
+      <c r="A18" s="15" t="n">
         <v>46121</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="n">
+      <c r="B18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D18" s="16" t="n">
         <v>0.9986111111111111</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Services Affected (to date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Detailed Incidents (to date)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>1. April 08, 2026 - Multiple Outages (3 minutes total)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Service 1: Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-    </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Service 2: Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Time: 4:09 AM GMT-4:12 AM GMT</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>1. April 16, 2026 - Outage (10 minutes)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>Service: Fortify on Demand API - EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Time: 2:26 PM GMT-2:36 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
           <t>Impact: Brief service disruption</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>2. April 09, 2026 - Outage (2 minutes)</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Service: SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Time: 7:11 PM GMT-7:13 PM GMT</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2. April 16, 2026 - Outage (10 minutes)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Service: Fortify on Demand Tenant Portal - EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Time: 2:28 PM GMT-2:38 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>3. April 08, 2026 - Multiple Outages (3 minutes total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Service 1: Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Service 2: Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Time: 4:09 AM GMT-4:12 AM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>4. April 09, 2026 - Outage (2 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Time: 7:11 PM GMT-7:13 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Impact: Brief service disruption</t>
         </is>
@@ -2392,13 +3766,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2410,32 +3784,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Start Date Time</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>End Date Time</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>Duration Minutes</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
@@ -2444,26 +3818,26 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -2474,26 +3848,26 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -2504,26 +3878,26 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -2539,12 +3913,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -2553,7 +3927,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -2569,17 +3943,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -2594,26 +3968,26 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -2624,26 +3998,26 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -2654,17 +4028,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2673,7 +4047,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -2684,26 +4058,26 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -2719,25 +4093,25 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -2749,25 +4123,25 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -2779,21 +4153,21 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -2809,21 +4183,21 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -2839,21 +4213,21 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -2869,21 +4243,21 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -2909,7 +4283,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -2939,7 +4313,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -2959,21 +4333,21 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -2989,21 +4363,21 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -3019,21 +4393,21 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -3049,21 +4423,21 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -3074,26 +4448,26 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -3109,21 +4483,21 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -3134,26 +4508,26 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>198</v>
+        <v>3</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -3164,26 +4538,26 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -3194,26 +4568,26 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>4</v>
+        <v>198</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -3229,21 +4603,21 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -3254,26 +4628,26 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -3284,26 +4658,26 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -3319,21 +4693,21 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -3349,21 +4723,21 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -3379,21 +4753,21 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -3409,21 +4783,21 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -3439,21 +4813,21 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -3469,21 +4843,21 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -3509,7 +4883,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
@@ -3539,7 +4913,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -3554,26 +4928,26 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -3584,26 +4958,26 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -3619,12 +4993,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -3633,7 +5007,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -3649,12 +5023,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -3663,7 +5037,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -3679,12 +5053,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3693,7 +5067,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -3709,81 +5083,81 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>207</v>
+        <v>1</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>207</v>
+        <v>5</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -3799,21 +5173,21 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -3829,21 +5203,21 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -3854,26 +5228,26 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -3884,26 +5258,26 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
@@ -3914,26 +5288,26 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>282</v>
+        <v>2</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -3944,26 +5318,26 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>282</v>
+        <v>2</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -3979,21 +5353,21 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>127</v>
+        <v>282</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
@@ -4009,21 +5383,21 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>127</v>
+        <v>282</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
@@ -4039,21 +5413,21 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
@@ -4069,21 +5443,21 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
@@ -4099,21 +5473,21 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
@@ -4129,21 +5503,21 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
@@ -4159,12 +5533,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -4173,11 +5547,11 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>4234</v>
+        <v>88</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -4189,12 +5563,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -4203,37 +5577,37 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4234</v>
+        <v>88</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>4234</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
@@ -4244,26 +5618,26 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>4234</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -4274,26 +5648,26 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-01-27T14:46:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1595</v>
+        <v>1</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -4304,26 +5678,26 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-01-27T14:45:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1595</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -4339,21 +5713,21 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>4982</v>
+        <v>1595</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -4364,26 +5738,26 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>1595</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -4399,21 +5773,21 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-01-16T16:24:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1070</v>
+        <v>4982</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
@@ -4429,17 +5803,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-01-16T15:14:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -4454,26 +5828,26 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-01-15T21:13:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>1070</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
@@ -4484,26 +5858,26 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-15T04:24:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
@@ -4514,26 +5888,26 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-10T15:08:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -4549,21 +5923,21 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-08T04:54:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
@@ -4579,21 +5953,21 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-08T04:54:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
@@ -4609,21 +5983,21 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-01-08T01:13:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
@@ -4639,360 +6013,92 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E77" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>Report revised: April 16, 2026</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Component Contains</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>FedRAMP Portal</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>FedRAMP</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>FedRAMP API</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>FedRAMP</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>AMS Portal</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>AMS</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>API - AMS</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>AMS API</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>AMS</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>EMEA Portal</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>API - EMEA</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>EMEA API</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - APAC</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>APAC Portal</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>APAC</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>API - APAC</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>APAC API</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>APAC</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - SGP</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>APAC/SGP Portal</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>APAC/SGP</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>API - SGP</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>APAC/SGP API</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>APAC/SGP</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Vulncat</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Vulncat</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>EU SAST Aviator</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>AMS SAST Aviator</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>AMS</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator</t>
         </is>
       </c>
     </row>
@@ -5007,7 +6113,401 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A113"/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Component Contains</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP Portal</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP API</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AMS Portal</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>API - AMS</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AMS API</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>EMEA Portal</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>API - EMEA</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>EMEA API</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - APAC</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>APAC Portal</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>API - APAC</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>APAC API</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>SGP Portal</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>API - SGP</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>SGP API</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Vulncat</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Vulncat</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>EU SAST Aviator</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>AMS SAST Aviator</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - EU</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>EU Portal</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>API - EU</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>EU API</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Debricked Fortify Integration</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Debricked Fortify Integration</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -5051,7 +6551,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: April 16, 2026 (mid-month update; April data through Apr 16; events added: Apr 7 AMS Portal degradation, Apr 8 FedRAMP outage 3 min, Apr 9 EU SAST outage 2 min, Apr 9-10 SAST maintenance windows).</t>
+          <t>Last updated: April 16, 2026 (mid-month update; April data through Apr 16; events added: Apr 7 AMS Portal degradation, Apr 8 FedRAMP outage 3 min, Apr 9 EU SAST outage 2 min, Apr 9-10 SAST maintenance windows, Apr 16 EU Portal/API outages 10 min each).</t>
         </is>
       </c>
     </row>
@@ -5243,97 +6743,98 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BUCKET MAPPING</t>
+          <t>REGIONAL BREAKOUT TAB</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>The 'Bucket Mapping' tab defines how raw component strings from the status page map to reporting buckets.</t>
+          <t>The 'Regional Breakout' tab provides per-component uptime percentages for every component tracked on status.fortify.com.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Buckets group by region (FedRAMP, AMS, EMEA, APAC, SGP) and type (Portal, API, SAST Aviator, Vulncat).</t>
+          <t>This tab does NOT use de-duplication. Each component's outage minutes are calculated independently.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>This mapping is used for per-bucket breakdowns if needed. The executive summary reports overall uptime.</t>
+          <t>This matches how status.fortify.com calculates and displays uptime per component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Only 'Outage' events count against uptime (consistent with the executive summary methodology).</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>FILE STRUCTURE</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>The tab has three sections: Core Services (Portal and API per region), SAST Aviator, and Other Services.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Tab layout and what each tab contains:</t>
+          <t>Monthly columns show Jan through Dec. The YTD column covers completed months only (same as the executive summary).</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [2026 Executive Summary]  -  The yearly roll-up. One table with all 12 months. YTD totals and SLA status.</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Added: April 2026.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Updated monthly. Future months show '-' until data is available.</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>BUCKET MAPPING</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">                               Key observations in column G. This is the tab leadership reads.</t>
+          <t>The 'Bucket Mapping' tab defines how raw component strings from the status page map to reporting buckets.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr"/>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Buckets group by region (FedRAMP, AMS, EMEA, APAC, SGP, EU) and type (Portal, API, SAST Aviator, Vulncat, Debricked Fortify Integration).</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  [Mon YYYY] (e.g. Jan 2026) - One tab per completed month. Contains: monthly summary block, daily outage table</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               (sorted worst-day-first), affected services list, and detailed incident write-ups.</t>
+          <t>This mapping is used for per-bucket breakdowns if needed. The executive summary reports overall uptime.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Each incident includes: date, services, time range, and impact assessment.</t>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>FILE STRUCTURE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">                               The current (in-progress) month tab shows partial data until month-end.</t>
+          <t>Tab layout and what each tab contains:</t>
         </is>
       </c>
     </row>
@@ -5343,21 +6844,21 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  [2026 Incident Data]       -  Raw event log. Every event (outage + maintenance) in reverse chronological order.</t>
+          <t xml:space="preserve">  [2026 Executive Summary]  -  The yearly roll-up. One table with all 12 months. YTD totals and SLA status.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">                               Columns: Event Type, Start Date Time (ISO), End Date Time, Service, Duration Minutes, Month.</t>
+          <t xml:space="preserve">                               Updated monthly. Future months show '-' until data is available.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">                               This is the fact table. New rows are appended here each month.</t>
+          <t xml:space="preserve">                               Key observations in column G. This is the tab leadership reads.</t>
         </is>
       </c>
     </row>
@@ -5367,320 +6868,403 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  [Bucket Mapping]           -  Reference table mapping component strings to region/service buckets.</t>
+          <t xml:space="preserve">  [Regional Breakout]        -  Per-component uptime percentages for every status page component.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">                               Used for per-bucket breakdowns. Rarely changes unless new services are added.</t>
+          <t xml:space="preserve">                               Three sections: Core Services (Portal/API by region), SAST Aviator, Other Services.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr"/>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Monthly columns plus YTD. No cross-component de-duplication.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  [Notes &amp; Methodology]      -  This tab. Calculation references, process documentation, and update instructions.</t>
+          <t xml:space="preserve">                               Numbers match status.fortify.com exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [Mon YYYY] (e.g. Jan 2026) - One tab per completed month. Contains: monthly summary block, daily outage table</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>HOW TO UPDATE THIS FILE EACH MONTH</t>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               (sorted worst-day-first), affected services list, and detailed incident write-ups.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Repeat these steps on or after the 1st of each new month. The goal is to finalize the prior month and set up the next.</t>
+          <t xml:space="preserve">                               Each incident includes: date, services, time range, and impact assessment.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr"/>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               The current (in-progress) month tab shows partial data until month-end.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Go to https://status.fortify.com/history and scroll to the month being finalized.</t>
-        </is>
-      </c>
+      <c r="A69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Capture every Outage and Maintenance event for that month. For each event, record:</t>
+          <t xml:space="preserve">  [2026 Incident Data]       -  Raw event log. Every event (outage + maintenance) in reverse chronological order.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     start time (GMT), end time (GMT), event type, and affected component string exactly as shown on the page.</t>
+          <t xml:space="preserve">                               Columns: Event Type, Start Date Time (ISO), End Date Time, Service, Duration Minutes, Month.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr"/>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               This is the fact table. New rows are appended here each month.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Append the new events as rows in the '2026 Incident Data' tab.</t>
-        </is>
-      </c>
+      <c r="A73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Use ISO format for start time (YYYY-MM-DDTHH:MM:SSZ). Match the existing column layout.</t>
+          <t xml:space="preserve">  [Bucket Mapping]           -  Reference table mapping component strings to region/service buckets.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr"/>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Used for per-bucket breakdowns. Rarely changes unless new services are added.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. For the month's detail tab (e.g., 'Mar 2026'):</t>
-        </is>
-      </c>
+      <c r="A76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - Finalize the Monthly Summary block (update outage count, minutes, uptime %).</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Build the Daily Outage Report table: aggregate outage incidents by date, sort by minutes descending.</t>
+          <t xml:space="preserve">  [Notes &amp; Methodology]      -  This tab. Calculation references, process documentation, and update instructions.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - List affected services.</t>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>HOW TO UPDATE THIS FILE EACH MONTH</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - Write up each incident: group simultaneous outages (start times within 60 seconds), note all affected services,</t>
+          <t>Repeat these steps on or after the 1st of each new month. The goal is to finalize the prior month and set up the next.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       time range, and a brief impact assessment.</t>
-        </is>
-      </c>
+      <c r="A81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - Remember: only 'Outage' events count. Maintenance is tracked but excluded from uptime.</t>
+          <t xml:space="preserve">  1. Go to https://status.fortify.com/history and scroll to the month being finalized.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr"/>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Capture every Outage and Maintenance event for that month. For each event, record:</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Create a new tab for the upcoming month (e.g., 'Apr 2026') with a placeholder/stub.</t>
+          <t xml:space="preserve">     start time (GMT), end time (GMT), event type, and affected component string exactly as shown on the page.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     It will be populated when that month closes.</t>
-        </is>
-      </c>
+      <c r="A85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr"/>
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Append the new events as rows in the '2026 Incident Data' tab.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Update the '2026 Executive Summary' tab:</t>
+          <t xml:space="preserve">     Use ISO format for start time (YYYY-MM-DDTHH:MM:SSZ). Match the existing column layout.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Fill in the newly completed month's row in the Monthly Uptime Summary table (count, minutes, hours, uptime %).</t>
-        </is>
-      </c>
+      <c r="A88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - Update the YTD TOTAL row to include the new month.</t>
+          <t xml:space="preserve">  3. For the month's detail tab (e.g., 'Mar 2026'):</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - Refresh Key Observations in column G if anything noteworthy happened.</t>
+          <t xml:space="preserve">     - Finalize the Monthly Summary block (update outage count, minutes, uptime %).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - Update the SLA Performance block at the bottom.</t>
+          <t xml:space="preserve">     - Build the Daily Outage Report table: aggregate outage incidents by date, sort by minutes descending.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr"/>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - List affected services.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. The de-duplication rule (grouping events within 60 seconds) and the uptime formulas above</t>
+          <t xml:space="preserve">     - Write up each incident: group simultaneous outages (start times within 60 seconds), note all affected services,</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     should be applied consistently. If you are using a tool or script to generate this, point it at the</t>
+          <t xml:space="preserve">       time range, and a brief impact assessment.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     status page URL, apply the same parsing logic, and follow this tab structure. The raw data tab</t>
+          <t xml:space="preserve">     - Remember: only 'Outage' events count. Maintenance is tracked but excluded from uptime.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     is the single source of truth; everything else derives from it.</t>
+      <c r="A96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Create a new tab for the upcoming month (e.g., 'Apr 2026') with a placeholder/stub.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>FORMATTING CONVENTIONS</t>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     It will be populated when that month closes.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Font: Aptos Narrow, 11pt body, 24pt title, 11pt bold for section headers</t>
-        </is>
-      </c>
+      <c r="A99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Table headers: white text on dark blue (#2F5496)</t>
+          <t xml:space="preserve">  5. Update the '2026 Executive Summary' tab:</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Uptime % format: 0.0000% (four decimals)</t>
+          <t xml:space="preserve">     - Fill in the newly completed month's row in the Monthly Uptime Summary table (count, minutes, hours, uptime %).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dates in daily tables: mm-dd-yy</t>
+          <t xml:space="preserve">     - Update the YTD TOTAL row to include the new month.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Month strings: YYYY-MM (e.g. 2026-01)</t>
+          <t xml:space="preserve">     - Refresh Key Observations in column G if anything noteworthy happened.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Daily table sort: outage minutes descending (worst day first)</t>
+          <t xml:space="preserve">     - Update the SLA Performance block at the bottom.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Incident write-ups: grouped by month, sorted by duration descending within each month</t>
+      <c r="A105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. The de-duplication rule (grouping events within 60 seconds) and the uptime formulas above</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>CONTACT / HISTORY</t>
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     should be applied consistently. If you are using a tool or script to generate this, point it at the</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>First created: February 19, 2026</t>
+          <t xml:space="preserve">     status page URL, apply the same parsing logic, and follow this tab structure. The raw data tab</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Last updated: April 16, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>Created by: Chance Bonner (cbonner@opentext.com)</t>
+          <t xml:space="preserve">     is the single source of truth; everything else derives from it.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>Source reference: Previous 2025 report was a separate deliverable; this file does not overlap with it.</t>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>FORMATTING CONVENTIONS</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Automation potential: The monthly update process follows a repeatable pattern and could be scripted.</t>
+          <t xml:space="preserve">  Font: Aptos Narrow, 11pt body, 24pt title, 11pt bold for section headers</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table headers: white text on dark blue (#2F5496)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Uptime % format: 0.0000% (four decimals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dates in daily tables: mm-dd-yy</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Month strings: YYYY-MM (e.g. 2026-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Daily table sort: outage minutes descending (worst day first)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Incident write-ups: grouped by month, sorted by duration descending within each month</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>CONTACT / HISTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>First created: February 19, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Last updated: April 16, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Created by: Chance Bonner (cbonner@opentext.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Source reference: Previous 2025 report was a separate deliverable; this file does not overlap with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Automation potential: The monthly update process follows a repeatable pattern and could be scripted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>The status page (status.fortify.com/history) is the canonical data source for all incident records.</t>
         </is>

--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -13,9 +13,10 @@
     <sheet name="Feb 2026" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Mar 2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Apr 2026" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2026 Incident Data" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Bucket Mapping" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Notes &amp; Methodology" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="May 2026" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026 Incident Data" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Bucket Mapping" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Notes &amp; Methodology" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,55 +544,55 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1. January: 4 outages (5 min); February: 3 outages (9 min); March: 7 outages (57 min)</t>
+          <t>1. January: 4 outages (5 min); February: 3 outages (9 min); March: 7 outages (57 min); April: 4 outages (25 min)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Completed Months: January - March 2026 (April in progress)</t>
+          <t>Completed Months: January - April 2026 (May in progress)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2. March 2 saw FedRAMP Portal/API hit with multiple back-to-back outages totaling 44 min, the highest single-day downtime in 2026</t>
+          <t>2. March 2 remains the worst single day in 2026 (FedRAMP Portal/API, 44 min); April 16 EU Portal/API outage (10 min) was the largest April incident</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>YTD Outages: 14 incidents (completed months)</t>
+          <t>YTD Outages: 18 incidents (completed months)</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>3. SAST Aviator (EU/AMS) logged outages on Mar 11, 13, 17, and 18, consistent with recurring brief disruption pattern from prior months</t>
+          <t>3. SAST Aviator (EU/AMS) continued brief outage pattern: Mar 11, 13, 17, 18 and Apr 9 (EU SAST, 2 min)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>YTD Outage Time: 71 minutes (1.18 hours) (completed months)</t>
+          <t>YTD Outage Time: 96 minutes (1.60 hours) (completed months)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>4. YTD uptime of 99.9452% continues to exceed the 99.9% SLA target across all three completed months</t>
+          <t>4. YTD uptime of 99.9444% continues to exceed the 99.9% SLA target across all four completed months</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>YTD Uptime: 99.9452% (completed months only)</t>
+          <t>YTD Uptime: 99.9444% (completed months only)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5. SAST Aviator (EU/AMS) accounts for the majority of incidents across all months; FedRAMP had the single worst day on Mar 2</t>
+          <t>5. SAST Aviator (EU/AMS) accounts for the majority of incidents across all months; FedRAMP had the single worst day on Mar 2 (44 min)</t>
         </is>
       </c>
     </row>
@@ -692,22 +693,16 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>4*</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>25*</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>0.42*</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="n">
+      <c r="B18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E18" s="6" t="n">
         <v>0.9994212962962963</v>
       </c>
     </row>
@@ -719,23 +714,21 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0*</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0*</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0.0*</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -934,71 +927,71 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.9994521604938271</v>
+        <v>0.9994444444444445</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* April 2026 is in progress. Partial data through April 16, 2026. Uptime % will change as month completes.</t>
+          <t>* May 2026 is in progress. Data will be finalized after May 31, 2026.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026 SLA Performance (Completed Months: Jan - Mar)</t>
+          <t>2026 SLA Performance (Completed Months: Jan - Apr)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Total Period Minutes (completed): 129,600</t>
+          <t>Total Period Minutes (completed): 172,800</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Total Outage Minutes: 71</t>
+          <t>Total Outage Minutes: 96</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Uptime Minutes: 129,529</t>
+          <t>Uptime Minutes: 172,704</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Uptime Percentage: 99.9452%</t>
+          <t>Uptime Percentage: 99.9444%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Outage Count: 14 incidents</t>
+          <t>Outage Count: 18 incidents</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Average Outage Duration: 5.07 minutes</t>
+          <t>Average Outage Duration: 5.33 minutes</t>
         </is>
       </c>
     </row>
@@ -1013,6 +1006,780 @@
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>SLA Status: MEETING TARGET</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A126"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Uptime Report: Notes &amp; Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ABOUT THIS FILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>This workbook is the 2026 Fortify on Demand uptime report. It is structured for monthly updates and yearly rollup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>It was first created in February 2026 using data scraped from https://status.fortify.com/history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>A prior report covering September 2024 - September 2025 was produced separately. This file starts fresh at 2026 to avoid overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Last updated: May 2, 2026 (April finalized; April complete through Apr 30; events added Apr 17-30: AMS maintenance Apr 17-20, EU maintenance Apr 21-22, EMEA maintenance Apr 24, multi-region maintenance Apr 29-30; no new outages Apr 17-30).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>DATA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>All incident data is sourced from: https://status.fortify.com/history</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>The history page lists events in reverse chronological order with: event type, date/time range (GMT), and affected service(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Each event row on the page shows one component. When a single incident affects multiple components (e.g., Portal + API),</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>both appear as separate lines with the same or near-same start time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>WHAT COUNTS TOWARD UPTIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Only 'Outage' type events are included in the uptime calculation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>'Maintenance' events are tracked in the raw data tab but excluded from uptime math.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>'Service Degradation' events are excluded from uptime. The portal and services are still available during degradation,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>so these do not represent true downtime. If a degradation event needs to be counted in the future, add it as a separate metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>'Disaster Recovery Exercise' events are informational only and excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>DE-DUPLICATION LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>When the same incident hits multiple components simultaneously (e.g., FedRAMP Portal and FedRAMP API both go down at 2:45 PM),</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>these are grouped into a single incident for counting purposes. The rule:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - If two or more outage events have start times within 60 seconds of each other, they are treated as one incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - The duration used is the MAX duration across the grouped components (not the sum).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - All affected component names are preserved in the detail write-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>This prevents double-counting when Portal + API go down together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>UPTIME FORMULA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Monthly Uptime % = 1 - (Total Outage Minutes in Month / Total Minutes in Month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Daily Uptime %   = 1 - (Outage Minutes on Day / 1440)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  YTD Uptime %     = 1 - (Sum of Outage Minutes for Completed Months / Sum of Total Minutes for Completed Months)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Minutes per month: Jan=44640, Feb=40320, Mar=44640, Apr=43200, May=44640, Jun=43200,</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                     Jul=44640, Aug=44640, Sep=43200, Oct=44640, Nov=43200, Dec=44640</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Minutes per day:   1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SLA target:        99.9% (43.8 minutes of allowed downtime per month on a 30-day month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>REGIONAL BREAKOUT TAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>The 'Regional Breakout' tab provides per-component uptime percentages for every component tracked on status.fortify.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>This tab does NOT use de-duplication. Each component's outage minutes are calculated independently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>This matches how status.fortify.com calculates and displays uptime per component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Only 'Outage' events count against uptime (consistent with the executive summary methodology).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>The tab has three sections: Core Services (Portal and API per region), SAST Aviator, and Other Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Monthly columns show Jan through Dec. The YTD column covers completed months only (same as the executive summary).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Added: April 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>BUCKET MAPPING</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>The 'Bucket Mapping' tab defines how raw component strings from the status page map to reporting buckets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Buckets group by region (FedRAMP, AMS, EMEA, APAC, SGP, EU) and type (Portal, API, SAST Aviator, Vulncat, Debricked Fortify Integration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>This mapping is used for per-bucket breakdowns if needed. The executive summary reports overall uptime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>FILE STRUCTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Tab layout and what each tab contains:</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [2026 Executive Summary]  -  The yearly roll-up. One table with all 12 months. YTD totals and SLA status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Updated monthly. Future months show '-' until data is available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Key observations in column G. This is the tab leadership reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [Regional Breakout]        -  Per-component uptime percentages for every status page component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Three sections: Core Services (Portal/API by region), SAST Aviator, Other Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Monthly columns plus YTD. No cross-component de-duplication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Numbers match status.fortify.com exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [Mon YYYY] (e.g. Jan 2026) - One tab per completed month. Contains: monthly summary block, daily outage table</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               (sorted worst-day-first), affected services list, and detailed incident write-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Each incident includes: date, services, time range, and impact assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               The current (in-progress) month tab shows partial data until month-end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [2026 Incident Data]       -  Raw event log. Every event (outage + maintenance) in reverse chronological order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Columns: Event Type, Start Date Time (ISO), End Date Time, Service, Duration Minutes, Month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               This is the fact table. New rows are appended here each month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [Bucket Mapping]           -  Reference table mapping component strings to region/service buckets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                               Used for per-bucket breakdowns. Rarely changes unless new services are added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [Notes &amp; Methodology]      -  This tab. Calculation references, process documentation, and update instructions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>HOW TO UPDATE THIS FILE EACH MONTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Repeat these steps on or after the 1st of each new month. The goal is to finalize the prior month and set up the next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Go to https://status.fortify.com/history and scroll to the month being finalized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Capture every Outage and Maintenance event for that month. For each event, record:</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     start time (GMT), end time (GMT), event type, and affected component string exactly as shown on the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Append the new events as rows in the '2026 Incident Data' tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Use ISO format for start time (YYYY-MM-DDTHH:MM:SSZ). Match the existing column layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. For the month's detail tab (e.g., 'Mar 2026'):</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Finalize the Monthly Summary block (update outage count, minutes, uptime %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Build the Daily Outage Report table: aggregate outage incidents by date, sort by minutes descending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - List affected services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Write up each incident: group simultaneous outages (start times within 60 seconds), note all affected services,</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       time range, and a brief impact assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Remember: only 'Outage' events count. Maintenance is tracked but excluded from uptime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Create a new tab for the upcoming month (e.g., 'Apr 2026') with a placeholder/stub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     It will be populated when that month closes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Update the '2026 Executive Summary' tab:</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Fill in the newly completed month's row in the Monthly Uptime Summary table (count, minutes, hours, uptime %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Update the YTD TOTAL row to include the new month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Refresh Key Observations in column G if anything noteworthy happened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Update the SLA Performance block at the bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. The de-duplication rule (grouping events within 60 seconds) and the uptime formulas above</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     should be applied consistently. If you are using a tool or script to generate this, point it at the</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     status page URL, apply the same parsing logic, and follow this tab structure. The raw data tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     is the single source of truth; everything else derives from it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>FORMATTING CONVENTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Font: Aptos Narrow, 11pt body, 24pt title, 11pt bold for section headers</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table headers: white text on dark blue (#2F5496)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Uptime % format: 0.0000% (four decimals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dates in daily tables: mm-dd-yy</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Month strings: YYYY-MM (e.g. 2026-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Daily table sort: outage minutes descending (worst day first)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Incident write-ups: grouped by month, sorted by duration descending within each month</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>CONTACT / HISTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>First created: February 19, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Last updated: May 2, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Created by: Chance Bonner (cbonner@opentext.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Source reference: Previous 2025 report was a separate deliverable; this file does not overlap with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Automation potential: The monthly update process follows a repeatable pattern and could be scripted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>The status page (status.fortify.com/history) is the canonical data source for all incident records.</t>
         </is>
       </c>
     </row>
@@ -1147,13 +1914,11 @@
       <c r="D5" s="12" t="n">
         <v>0.9990367383512545</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="12" t="n">
         <v>0.9999305555555555</v>
       </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -1191,7 +1956,7 @@
         </is>
       </c>
       <c r="N5" s="12" t="n">
-        <v>0.9996604938271605</v>
+        <v>0.9997280092592593</v>
       </c>
     </row>
     <row r="6">
@@ -1209,13 +1974,11 @@
       <c r="D6" s="12" t="n">
         <v>0.9998431899641577</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.9999537037037037</v>
       </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -1253,7 +2016,7 @@
         </is>
       </c>
       <c r="N6" s="12" t="n">
-        <v>0.9999382716049383</v>
+        <v>0.9999421296296296</v>
       </c>
     </row>
     <row r="7">
@@ -1271,13 +2034,11 @@
       <c r="D7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1333,13 +2094,11 @@
       <c r="D8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1395,13 +2154,11 @@
       <c r="D9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1457,13 +2214,11 @@
       <c r="D10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
@@ -1519,13 +2274,11 @@
       <c r="D11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1581,13 +2334,11 @@
       <c r="D12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1643,13 +2394,11 @@
       <c r="D13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1705,13 +2454,11 @@
       <c r="D14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1749,7 +2496,7 @@
         </is>
       </c>
       <c r="N14" s="12" t="n">
-        <v>0.9999614197530864</v>
+        <v>0.9999710648148148</v>
       </c>
     </row>
     <row r="15">
@@ -1767,13 +2514,11 @@
       <c r="D15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.9997685185185186</v>
       </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1811,7 +2556,7 @@
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>0.9999421296296296</v>
       </c>
     </row>
     <row r="16">
@@ -1829,13 +2574,11 @@
       <c r="D16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="12" t="n">
         <v>0.9997685185185186</v>
       </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1873,7 +2616,7 @@
         </is>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1</v>
+        <v>0.9999421296296296</v>
       </c>
     </row>
     <row r="18">
@@ -1970,13 +2713,11 @@
       <c r="D20" s="12" t="n">
         <v>0.9997535842293906</v>
       </c>
-      <c r="E20" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -2014,7 +2755,7 @@
         </is>
       </c>
       <c r="N20" s="12" t="n">
-        <v>0.9998996913580247</v>
+        <v>0.9999247685185185</v>
       </c>
     </row>
     <row r="21">
@@ -2032,13 +2773,11 @@
       <c r="D21" s="12" t="n">
         <v>0.9999551971326165</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="12" t="n">
         <v>0.9999537037037037</v>
       </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -2076,7 +2815,7 @@
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>0.999945987654321</v>
+        <v>0.9999479166666667</v>
       </c>
     </row>
     <row r="23">
@@ -2173,13 +2912,11 @@
       <c r="D25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -2235,13 +2972,11 @@
       <c r="D26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -2279,13 +3014,13 @@
         </is>
       </c>
       <c r="N26" s="12" t="n">
-        <v>0.9999922839506172</v>
+        <v>0.999994212962963</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* April 2026 is in progress. Partial data shown in italics.</t>
+          <t>* May 2026 is in progress. Partial data shown in italics.</t>
         </is>
       </c>
     </row>
@@ -3418,7 +4153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3432,330 +4167,323 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>April 2026 - Monthly Detail (Partial)</t>
+          <t>April 2026 - Monthly Detail</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Month in progress. Partial data through April 16, 2026. To be finalized after April 30.</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Summary</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Monthly Summary (Partial)</t>
+          <t>Period:</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>April 1 - 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Total Minutes:</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>43,200</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Period:</t>
+          <t>Outage Count:</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>April 1 - 30, 2026</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Total Minutes:</t>
+          <t>Outage Minutes:</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>43,200</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Outage Count (to date):</t>
+          <t>Uptime %:</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>99.9421%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Outage Minutes (to date):</t>
+          <t>SLA Status:</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Uptime % (partial, not final):</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>99.9421%</t>
+          <t>MEETING TARGET (99.9%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Status:</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>IN PROGRESS, partial data through April 16, 2026</t>
+          <t>Daily Outage Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Outage Count</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Outage Minutes</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Uptime Percentage</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Daily Outage Report (Partial)</t>
-        </is>
+      <c r="A14" s="15" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0.9861111111111112</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Outage Count</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Outage Minutes</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Uptime Percentage</t>
-        </is>
+      <c r="A15" s="15" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>0.9979166666666667</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46128</v>
+        <v>46121</v>
       </c>
       <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>20</v>
-      </c>
       <c r="D16" s="16" t="n">
-        <v>0.9861111111111112</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="n">
-        <v>46120</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>0.9979166666666667</v>
+        <v>0.9986111111111111</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
-        <v>46121</v>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>0.9986111111111111</v>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Services Affected</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Services Affected (to date)</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
           <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Detailed Incidents</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Detailed Incidents (to date)</t>
+          <t>1. April 16, 2026 - Outage (10 minutes)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>1. April 16, 2026 - Outage (10 minutes)</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Service: Fortify on Demand API - EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Time: 2:26 PM GMT-2:36 PM GMT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Service: Fortify on Demand API - EU</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Time: 2:26 PM GMT-2:36 PM GMT</t>
+          <t>Impact: Brief service disruption</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Impact: Brief service disruption</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2. April 16, 2026 - Outage (10 minutes)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>2. April 16, 2026 - Outage (10 minutes)</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Service: Fortify on Demand Tenant Portal - EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Time: 2:28 PM GMT-2:38 PM GMT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Service: Fortify on Demand Tenant Portal - EU</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Time: 2:28 PM GMT-2:38 PM GMT</t>
+          <t>Impact: Brief service disruption</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Impact: Brief service disruption</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>3. April 08, 2026 - Multiple Outages (3 minutes total)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>3. April 08, 2026 - Multiple Outages (3 minutes total)</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Service 1: Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Service 2: Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Service 1: Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Time: 4:09 AM GMT-4:12 AM GMT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Service 2: Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Time: 4:09 AM GMT-4:12 AM GMT</t>
+          <t>Impact: Brief service disruption</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Impact: Brief service disruption</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>4. April 09, 2026 - Outage (2 minutes)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>4. April 09, 2026 - Outage (2 minutes)</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Time: 7:11 PM GMT-7:13 PM GMT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Service: SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Time: 7:11 PM GMT-7:13 PM GMT</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Impact: Brief service disruption</t>
         </is>
@@ -3772,7 +4500,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="85" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>May 2026 - Monthly Detail (Partial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Month in progress. To be finalized after May 31, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Summary (Partial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Period:</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>May 1 - 31, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Total Minutes:</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>44,640</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Outage Count (to date):</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Outage Minutes (to date):</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Uptime % (partial, not final):</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>100.0000%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Status:</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Daily Outage Report (Partial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Outage Count</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Outage Minutes</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Uptime Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Services Affected (to date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Detailed Incidents (to date)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3818,26 +4704,26 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:28:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -3848,26 +4734,26 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:26:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -3883,21 +4769,21 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -3913,21 +4799,21 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -3938,26 +4824,26 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -3973,21 +4859,21 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>211</v>
+        <v>88</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -3998,26 +4884,26 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -4028,26 +4914,26 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -4058,26 +4944,26 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -4093,21 +4979,21 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>50</v>
+        <v>273</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -4123,21 +5009,21 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>50</v>
+        <v>273</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -4153,25 +5039,25 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4183,25 +5069,25 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4213,25 +5099,25 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4243,25 +5129,25 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>150</v>
+        <v>1187</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4273,25 +5159,25 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>123</v>
+        <v>1187</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4303,25 +5189,25 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>123</v>
+        <v>4284</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4333,85 +5219,85 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>123</v>
+        <v>4284</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4423,25 +5309,25 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4453,235 +5339,235 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>198</v>
+        <v>3</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4693,12 +5579,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -4707,7 +5593,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -4723,12 +5609,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -4737,7 +5623,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -4753,21 +5639,21 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -4783,21 +5669,21 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -4813,21 +5699,21 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -4843,21 +5729,21 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -4873,21 +5759,21 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -4903,21 +5789,21 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -4933,21 +5819,21 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -4963,21 +5849,21 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -4988,26 +5874,26 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -5018,26 +5904,26 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -5053,21 +5939,21 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -5078,26 +5964,26 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
@@ -5108,26 +5994,26 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -5143,85 +6029,85 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>207</v>
+        <v>4</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>207</v>
+        <v>4</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5233,12 +6119,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -5247,11 +6133,11 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5263,12 +6149,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -5277,71 +6163,71 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5353,25 +6239,25 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>282</v>
+        <v>87</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5383,25 +6269,25 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>282</v>
+        <v>87</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5413,25 +6299,25 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5443,25 +6329,25 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5473,25 +6359,25 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5503,145 +6389,145 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4234</v>
+        <v>31</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>4234</v>
+        <v>2</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5653,17 +6539,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -5671,7 +6557,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5683,25 +6569,25 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5713,25 +6599,25 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1595</v>
+        <v>207</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5743,25 +6629,25 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1595</v>
+        <v>207</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5773,85 +6659,85 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>4982</v>
+        <v>159</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1070</v>
+        <v>2</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5863,55 +6749,55 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>2</v>
+        <v>282</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5923,25 +6809,25 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>140</v>
+        <v>282</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5953,25 +6839,25 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5983,25 +6869,25 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -6013,25 +6899,25 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -6043,25 +6929,25 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -6073,32 +6959,572 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
+          <t>2026-02-04T23:58:00Z</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-04T23:58:00Z</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30T19:08:00Z</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30T19:08:00Z</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:46:00Z</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:45:00Z</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T16:24:00Z</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>4982</v>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T15:14:00Z</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T21:13:00Z</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:24:00Z</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-10T15:08:00Z</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="E95" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: April 16, 2026</t>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: May 02, 2026</t>
         </is>
       </c>
     </row>
@@ -6107,7 +7533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6499,778 +7925,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A126"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Fortify on Demand - Uptime Report: Notes &amp; Methodology</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ABOUT THIS FILE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>This workbook is the 2026 Fortify on Demand uptime report. It is structured for monthly updates and yearly rollup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>It was first created in February 2026 using data scraped from https://status.fortify.com/history.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>A prior report covering September 2024 - September 2025 was produced separately. This file starts fresh at 2026 to avoid overlap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Last updated: April 16, 2026 (mid-month update; April data through Apr 16; events added: Apr 7 AMS Portal degradation, Apr 8 FedRAMP outage 3 min, Apr 9 EU SAST outage 2 min, Apr 9-10 SAST maintenance windows, Apr 16 EU Portal/API outages 10 min each).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>DATA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>All incident data is sourced from: https://status.fortify.com/history</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>The history page lists events in reverse chronological order with: event type, date/time range (GMT), and affected service(s).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Each event row on the page shows one component. When a single incident affects multiple components (e.g., Portal + API),</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>both appear as separate lines with the same or near-same start time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>WHAT COUNTS TOWARD UPTIME</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Only 'Outage' type events are included in the uptime calculation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>'Maintenance' events are tracked in the raw data tab but excluded from uptime math.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>'Service Degradation' events are excluded from uptime. The portal and services are still available during degradation,</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>so these do not represent true downtime. If a degradation event needs to be counted in the future, add it as a separate metric.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>'Disaster Recovery Exercise' events are informational only and excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>DE-DUPLICATION LOGIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>When the same incident hits multiple components simultaneously (e.g., FedRAMP Portal and FedRAMP API both go down at 2:45 PM),</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>these are grouped into a single incident for counting purposes. The rule:</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - If two or more outage events have start times within 60 seconds of each other, they are treated as one incident.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - The duration used is the MAX duration across the grouped components (not the sum).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - All affected component names are preserved in the detail write-up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>This prevents double-counting when Portal + API go down together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>UPTIME FORMULA</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Monthly Uptime % = 1 - (Total Outage Minutes in Month / Total Minutes in Month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Daily Uptime %   = 1 - (Outage Minutes on Day / 1440)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  YTD Uptime %     = 1 - (Sum of Outage Minutes for Completed Months / Sum of Total Minutes for Completed Months)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Minutes per month: Jan=44640, Feb=40320, Mar=44640, Apr=43200, May=44640, Jun=43200,</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                     Jul=44640, Aug=44640, Sep=43200, Oct=44640, Nov=43200, Dec=44640</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Minutes per day:   1440</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SLA target:        99.9% (43.8 minutes of allowed downtime per month on a 30-day month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>REGIONAL BREAKOUT TAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>The 'Regional Breakout' tab provides per-component uptime percentages for every component tracked on status.fortify.com.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>This tab does NOT use de-duplication. Each component's outage minutes are calculated independently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>This matches how status.fortify.com calculates and displays uptime per component.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Only 'Outage' events count against uptime (consistent with the executive summary methodology).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>The tab has three sections: Core Services (Portal and API per region), SAST Aviator, and Other Services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Monthly columns show Jan through Dec. The YTD column covers completed months only (same as the executive summary).</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Added: April 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>BUCKET MAPPING</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>The 'Bucket Mapping' tab defines how raw component strings from the status page map to reporting buckets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Buckets group by region (FedRAMP, AMS, EMEA, APAC, SGP, EU) and type (Portal, API, SAST Aviator, Vulncat, Debricked Fortify Integration).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>This mapping is used for per-bucket breakdowns if needed. The executive summary reports overall uptime.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>FILE STRUCTURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Tab layout and what each tab contains:</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [2026 Executive Summary]  -  The yearly roll-up. One table with all 12 months. YTD totals and SLA status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Updated monthly. Future months show '-' until data is available.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Key observations in column G. This is the tab leadership reads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [Regional Breakout]        -  Per-component uptime percentages for every status page component.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Three sections: Core Services (Portal/API by region), SAST Aviator, Other Services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Monthly columns plus YTD. No cross-component de-duplication.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Numbers match status.fortify.com exactly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [Mon YYYY] (e.g. Jan 2026) - One tab per completed month. Contains: monthly summary block, daily outage table</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               (sorted worst-day-first), affected services list, and detailed incident write-ups.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Each incident includes: date, services, time range, and impact assessment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               The current (in-progress) month tab shows partial data until month-end.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [2026 Incident Data]       -  Raw event log. Every event (outage + maintenance) in reverse chronological order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Columns: Event Type, Start Date Time (ISO), End Date Time, Service, Duration Minutes, Month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               This is the fact table. New rows are appended here each month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [Bucket Mapping]           -  Reference table mapping component strings to region/service buckets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                               Used for per-bucket breakdowns. Rarely changes unless new services are added.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [Notes &amp; Methodology]      -  This tab. Calculation references, process documentation, and update instructions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>HOW TO UPDATE THIS FILE EACH MONTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>Repeat these steps on or after the 1st of each new month. The goal is to finalize the prior month and set up the next.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Go to https://status.fortify.com/history and scroll to the month being finalized.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Capture every Outage and Maintenance event for that month. For each event, record:</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     start time (GMT), end time (GMT), event type, and affected component string exactly as shown on the page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Append the new events as rows in the '2026 Incident Data' tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Use ISO format for start time (YYYY-MM-DDTHH:MM:SSZ). Match the existing column layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. For the month's detail tab (e.g., 'Mar 2026'):</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Finalize the Monthly Summary block (update outage count, minutes, uptime %).</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Build the Daily Outage Report table: aggregate outage incidents by date, sort by minutes descending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - List affected services.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Write up each incident: group simultaneous outages (start times within 60 seconds), note all affected services,</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       time range, and a brief impact assessment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Remember: only 'Outage' events count. Maintenance is tracked but excluded from uptime.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. Create a new tab for the upcoming month (e.g., 'Apr 2026') with a placeholder/stub.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     It will be populated when that month closes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. Update the '2026 Executive Summary' tab:</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Fill in the newly completed month's row in the Monthly Uptime Summary table (count, minutes, hours, uptime %).</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Update the YTD TOTAL row to include the new month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Refresh Key Observations in column G if anything noteworthy happened.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Update the SLA Performance block at the bottom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6. The de-duplication rule (grouping events within 60 seconds) and the uptime formulas above</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     should be applied consistently. If you are using a tool or script to generate this, point it at the</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     status page URL, apply the same parsing logic, and follow this tab structure. The raw data tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     is the single source of truth; everything else derives from it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>FORMATTING CONVENTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Font: Aptos Narrow, 11pt body, 24pt title, 11pt bold for section headers</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Table headers: white text on dark blue (#2F5496)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Uptime % format: 0.0000% (four decimals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Dates in daily tables: mm-dd-yy</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Month strings: YYYY-MM (e.g. 2026-01)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Daily table sort: outage minutes descending (worst day first)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Incident write-ups: grouped by month, sorted by duration descending within each month</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>CONTACT / HISTORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>First created: February 19, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>Last updated: April 16, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>Created by: Chance Bonner (cbonner@opentext.com)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>Source reference: Previous 2025 report was a separate deliverable; this file does not overlap with it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>Automation potential: The monthly update process follows a repeatable pattern and could be scripted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>The status page (status.fortify.com/history) is the canonical data source for all incident records.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Completed Months: January - April 2026 (May in progress)</t>
+          <t>Completed Months: January - April 2026 (May in progress, partial through May 16)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -714,21 +714,21 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>0*</t>
+          <t>2*</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>0*</t>
+          <t>4*</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>0.0*</t>
+          <t>0.07*</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1</v>
+        <v>0.999910394265233</v>
       </c>
     </row>
     <row r="20">
@@ -942,7 +942,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* May 2026 is in progress. Data will be finalized after May 31, 2026.</t>
+          <t>* May 2026 is in progress. Partial data through May 16, 2026. Will be finalized after May 31, 2026.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: May 2, 2026 (April finalized; April complete through Apr 30; events added Apr 17-30: AMS maintenance Apr 17-20, EU maintenance Apr 21-22, EMEA maintenance Apr 24, multi-region maintenance Apr 29-30; no new outages Apr 17-30).</t>
+          <t>Last updated: May 16, 2026 (mid-month snapshot through May 16; 2 outages added: AMS SAST Aviator May 10 2 min, EU SAST Aviator May 9 2 min; maintenance added: APAC May 4, AMS May 8, SGP May 11-12; service degradation events: AMS May 7-8 and May 13; Apr 22 - May 4 AMS service degradation back-filled to April data).</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Last updated: May 2, 2026</t>
+          <t>Last updated: May 16, 2026</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>1</v>
+        <v>0.9999551971326165</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>0.9999537037037037</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>1</v>
+        <v>0.9999551971326165</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4521,7 +4521,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Month in progress. To be finalized after May 31, 2026.</t>
+          <t>Month in progress. Partial data through May 16, 2026. To be finalized after May 31, 2026.</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>100.0000%</t>
+          <t>99.9910%</t>
         </is>
       </c>
     </row>
@@ -4633,17 +4633,115 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>0.9986111111111111</v>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="15" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>0.9986111111111111</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Services Affected (to date)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Detailed Incidents (to date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>1. May 09, 2026 - Outage (2 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Time: 7:11 PM GMT-7:13 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2. May 10, 2026 - Outage (2 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Time: 9:09 PM GMT-9:11 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4704,17 +4802,17 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -4723,28 +4821,28 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -4753,11 +4851,11 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -4769,25 +4867,25 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>78</v>
+        <v>673</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -4799,85 +4897,85 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>78</v>
+        <v>673</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-10T21:09:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 10, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -4889,25 +4987,25 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -4919,85 +5017,85 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>273</v>
+        <v>1395</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>273</v>
+        <v>1395</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -5009,25 +5107,25 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>273</v>
+        <v>72</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -5039,25 +5137,25 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>273</v>
+        <v>72</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -5069,21 +5167,21 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -5099,21 +5197,21 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -5129,21 +5227,21 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1187</v>
+        <v>78</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -5159,21 +5257,21 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1187</v>
+        <v>78</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -5189,21 +5287,21 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>4284</v>
+        <v>88</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -5219,21 +5317,21 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>4284</v>
+        <v>88</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -5244,26 +5342,26 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:28:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -5274,26 +5372,26 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:26:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -5309,21 +5407,21 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>96</v>
+        <v>273</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -5339,21 +5437,21 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>30</v>
+        <v>273</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -5364,26 +5462,26 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>273</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -5399,21 +5497,21 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -5424,26 +5522,26 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>242</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -5454,26 +5552,26 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>242</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -5489,12 +5587,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -5503,7 +5601,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>78</v>
+        <v>17272</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -5514,26 +5612,26 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>50</v>
+        <v>17272</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -5549,21 +5647,21 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>50</v>
+        <v>1187</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -5579,25 +5677,25 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>203</v>
+        <v>1187</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5609,25 +5707,25 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>203</v>
+        <v>4284</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5639,85 +5737,85 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>150</v>
+        <v>4284</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5729,25 +5827,25 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5759,55 +5857,55 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5819,145 +5917,145 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5969,25 +6067,25 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5999,21 +6097,21 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -6024,26 +6122,26 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2</v>
+        <v>203</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -6054,26 +6152,26 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -6084,26 +6182,26 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -6119,21 +6217,21 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -6149,21 +6247,21 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
@@ -6179,21 +6277,21 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -6209,21 +6307,21 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -6239,21 +6337,21 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
@@ -6269,21 +6367,21 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
@@ -6299,21 +6397,21 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
@@ -6329,21 +6427,21 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
@@ -6354,26 +6452,26 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
@@ -6389,21 +6487,21 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
@@ -6414,26 +6512,26 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
@@ -6449,21 +6547,21 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
@@ -6479,21 +6577,21 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
@@ -6509,21 +6607,21 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -6534,26 +6632,26 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -6564,30 +6662,30 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -6599,25 +6697,25 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -6629,25 +6727,25 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -6659,25 +6757,25 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -6689,85 +6787,85 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6877,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -6793,11 +6891,11 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>282</v>
+        <v>95</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6907,12 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -6823,88 +6921,88 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>282</v>
+        <v>95</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -6913,28 +7011,28 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -6943,67 +7041,67 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
@@ -7019,25 +7117,25 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>4234</v>
+        <v>207</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7049,145 +7147,145 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>4234</v>
+        <v>207</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1595</v>
+        <v>2</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1595</v>
+        <v>2</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7199,55 +7297,55 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4982</v>
+        <v>282</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7259,85 +7357,85 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1070</v>
+        <v>127</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7349,25 +7447,25 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7379,25 +7477,25 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7409,25 +7507,25 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7439,21 +7537,21 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>137</v>
+        <v>4234</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
@@ -7469,21 +7567,21 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>38</v>
+        <v>4234</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
@@ -7494,37 +7592,457 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:46:00Z</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:45:00Z</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T16:24:00Z</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>4982</v>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T15:14:00Z</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T21:13:00Z</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:24:00Z</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-10T15:08:00Z</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n">
+      <c r="E109" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: May 02, 2026</t>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: May 16, 2026</t>
         </is>
       </c>
     </row>
